--- a/nursing/フォーマット/04_相談支援様式/02_モニタリング報告書.xlsx
+++ b/nursing/フォーマット/04_相談支援様式/02_モニタリング報告書.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,40 +26,46 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="FF0E7490"/>
-      <sz val="13"/>
+      <color rgb="00163A2B"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FF0E7490"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00163A2B"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <color rgb="00283129"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <i val="1"/>
-      <color rgb="FF6B7280"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -68,21 +74,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCFFAFE"/>
+        <fgColor rgb="00E4EFE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E7490"/>
+        <fgColor rgb="001F4D3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
+        <fgColor rgb="00A9854A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6EDDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -91,38 +102,77 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="medium">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DAD3C2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DAD3C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DAD3C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DAD3C2"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A9854A"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A9854A"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A9854A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00A9854A"/>
+      </left>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,250 +536,299 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>モニタリング報告書（継続サービス利用支援用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>モニタリング報告書（継続サービス利用支援）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>【モニタリング頻度】原則6ヶ月毎（状態変化時・サービス内容変更時は随時）。実施記録は保管し、計画の見直しに活用すること。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+          <t>計画の達成状況を定期確認。支給決定期間・本人状況により頻度を設定（標準は3〜6か月等）</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>利用者氏名</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>（様）</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>モニタリング実施日</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　月　日</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>相談支援専門員</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>前回モニタリング日</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　月　日</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>計画の対象期間</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　月〜　　年　月</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>参加者</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>本人 / 家族 / 事業所担当者</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>【目標の達成状況】（計画上の目標ごとに達成度を確認）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>目標①「　　　　　　　　　」　達成度：達成 / ほぼ達成 / 未達成
-→状況：
-目標②「　　　　　　　　　」　達成度：達成 / ほぼ達成 / 未達成
-→状況：</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>【各サービスの提供状況の確認】</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>就労継続支援：利用回数　日/月　体調・様子：
-訪問看護：利用回数　回/月　主な内容：
-その他：</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>【本人・家族の意向・満足度】</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>本人の意向：
-家族の意向：
-サービスへの満足度：満足 / ほぼ満足 / 不満　理由：</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>【生活状況の変化】</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>健康状態：
-生活環境：
-社会参加状況：</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>【支援上の課題・今後の方針】</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>課題：
-方針：
-計画変更の要否：要（変更内容：　　　） / 不要</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>【サービス等利用計画の変更内容（変更ある場合）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>【次回モニタリング予定】</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="25" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>次回：　　年　月頃（変化があれば随時実施）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>【本人・家族の確認】</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>モニタリング結果について説明を受け、確認しました。
-署名：　　　　　　　（続柄：　　）　日付：　　年　月　日</t>
-        </is>
-      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>前回計画作成日</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>実施方法</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>□自宅訪問　□来所　□電話　□その他</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="8" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>支援目標ごとの達成状況・本人の感想</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>支援目標</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>サービス提供状況</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>達成度</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>本人・家族の評価</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>今後の課題</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>見直し要否</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr"/>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="8" customHeight="1"/>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>計画変更の必要性</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>□現計画を継続　□計画の見直しが必要（理由：　　　　　　）</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>次回モニタリング予定</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>※ モニタリング結果は支給決定市町村へ提出。状況変化があれば計画を見直し、必要に応じてサービス担当者会議を再開催。</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A11:H11"/>
+  <mergeCells count="18">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C4:H4"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C20:H20"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>